--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:35</t>
+    <t xml:space="preserve">2026-09-09 22:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:20</t>
+    <t xml:space="preserve">2026-09-12 19:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:37</t>
+    <t xml:space="preserve">2026-09-24 00:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:14</t>
+    <t xml:space="preserve">2026-09-27 22:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:04</t>
+    <t xml:space="preserve">2026-09-29 10:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -508,7 +508,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>18.5</v>
+        <v>185.04</v>
       </c>
     </row>
     <row r="3">
@@ -525,7 +525,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>13.86</v>
+        <v>138.62</v>
       </c>
     </row>
     <row r="4">
@@ -542,7 +542,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>13.85</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="5">
@@ -559,7 +559,7 @@
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>13.19</v>
+        <v>131.87</v>
       </c>
     </row>
     <row r="6">
@@ -576,7 +576,7 @@
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>12.44</v>
+        <v>124.42</v>
       </c>
     </row>
     <row r="7">
@@ -593,7 +593,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>12.31</v>
+        <v>123.08</v>
       </c>
     </row>
     <row r="8">
@@ -610,7 +610,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>11.26</v>
+        <v>112.6</v>
       </c>
     </row>
     <row r="9">
@@ -627,7 +627,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>8.24</v>
+        <v>82.35</v>
       </c>
     </row>
     <row r="10">
@@ -644,7 +644,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7.54</v>
+        <v>75.44</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 10:58</t>
+    <t xml:space="preserve">2026-10-01 19:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -90,7 +90,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:23</t>
+    <t xml:space="preserve">2026-10-02 13:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2019_atacama.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:04</t>
+    <t xml:space="preserve">2026-10-05 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
